--- a/output/pdf_financials_xlsx/NEXG.xlsx
+++ b/output/pdf_financials_xlsx/NEXG.xlsx
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.047891</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>5.6e-05</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.001745</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.001223</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.529215</v>
       </c>
     </row>
     <row r="13">
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.998031</v>
+        <v>-3.045922</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.335483</v>
+        <v>-1.335539</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-5.838474</v>
@@ -2003,10 +2003,10 @@
         <v>-4.950671</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-4.761411</v>
+        <v>-4.763156</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-3.545633</v>
+        <v>-3.546856</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-15.925579</v>
@@ -2021,7 +2021,7 @@
         <v>-20.090191</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-42.080691</v>
+        <v>-41.551476</v>
       </c>
     </row>
     <row r="28">
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.998031</v>
+        <v>-3.045922</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.335483</v>
+        <v>-1.335539</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-5.838474</v>
@@ -2119,10 +2119,10 @@
         <v>-4.950671</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-4.761411</v>
+        <v>-4.763156</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-3.545633</v>
+        <v>-3.546856</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-15.925579</v>
@@ -2137,7 +2137,7 @@
         <v>-20.090191</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-42.080691</v>
+        <v>-41.551476</v>
       </c>
     </row>
     <row r="30">
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-519.2096941231889</v>
+        <v>-527.5036281956698</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-710.0233930565155</v>
+        <v>-710.0531660375352</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-1727.02194246094</v>
@@ -42318,7 +42318,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -46542,7 +46542,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -55414,7 +55414,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E475" s="5" t="n">

--- a/output/pdf_financials_xlsx/NEXG.xlsx
+++ b/output/pdf_financials_xlsx/NEXG.xlsx
@@ -1322,7 +1322,7 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.629</v>
+        <v>-0.629</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0.891556</v>
@@ -1334,19 +1334,19 @@
         <v>0.9624</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.302</v>
+        <v>-0.302</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.1573</v>
+        <v>-0.1573</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.3407</v>
+        <v>-0.3407</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.9694</v>
+        <v>-0.9694</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.6998</v>
+        <v>-1.6998</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>-0.2498</v>
@@ -2721,13 +2721,13 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.07459499999999999</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.094087</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.025424</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0</v>
@@ -2748,19 +2748,19 @@
         <v>0</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.004395</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.085755</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>0.10693</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>0.241974</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>0.393107</v>
       </c>
     </row>
     <row r="41">
@@ -2779,13 +2779,13 @@
         <v>0</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0</v>
+        <v>0.07459499999999999</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0</v>
+        <v>0.094087</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0</v>
+        <v>0.025424</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>0</v>
@@ -2806,19 +2806,19 @@
         <v>0</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>0</v>
+        <v>0.004395</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>0</v>
+        <v>0.085755</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0</v>
+        <v>0.10693</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>0</v>
+        <v>0.241974</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>0</v>
+        <v>0.393107</v>
       </c>
     </row>
     <row r="42">
@@ -3185,13 +3185,13 @@
         <v>0.130702</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.351685</v>
+        <v>0.27709</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.540133</v>
+        <v>0.446046</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.654268</v>
+        <v>0.628844</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.254261</v>
@@ -3212,19 +3212,19 @@
         <v>0.259281</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.741995</v>
+        <v>1.7376</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.820687</v>
+        <v>1.734932</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.252901</v>
+        <v>2.145971</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>5.963772</v>
+        <v>5.721798</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>23.883806</v>
+        <v>23.490699</v>
       </c>
     </row>
     <row r="49">
@@ -4222,19 +4222,19 @@
         <v>0</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.7053469999999999</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.523264</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.595315</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>1.89409</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>2.00092</v>
       </c>
     </row>
     <row r="65">
@@ -4375,40 +4375,40 @@
         <v>0</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.158185</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.149819</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.206889</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.44402</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.424208</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.274814</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.230659</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>1.018326</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.696105</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.523261</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>1.799912</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>2.804109</v>
       </c>
     </row>
     <row r="68">
@@ -7179,13 +7179,13 @@
         <v>0.644348</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.2583</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.469345</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.043749</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -7194,7 +7194,7 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.134995</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
@@ -7218,7 +7218,7 @@
         <v>0</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.002217</v>
       </c>
       <c r="R115" s="3" t="n">
         <v>0</v>
@@ -22956,7 +22956,11 @@
           <t>Proceeds from share issuance (Note 18)</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -25231,7 +25235,11 @@
           <t>Proceeds from sale of equity investments (Note 10)</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -28142,7 +28150,11 @@
           <t>Deferred income tax expense (recovery) (Note 16)</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -30721,7 +30733,11 @@
           <t>Deferred income tax recovery (Note 16)</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -31426,7 +31442,11 @@
           <t>Fair value of warrants issued for commission on private placement $</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -31620,7 +31640,11 @@
           <t>Deferred income tax recovery (Note 17)</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -34192,7 +34216,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -35095,7 +35123,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -36273,7 +36305,11 @@
           <t>Warrants/Options issued for commission on private placement $</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -36861,7 +36897,11 @@
           <t>Warrants/Options issued for commission on private placement $</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -37552,7 +37592,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -37746,7 +37790,11 @@
           <t>Options / Warrants issued for commission on private placement $</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -37845,7 +37893,11 @@
           <t>Shares issued for commission on private placement $</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -38645,7 +38697,11 @@
           <t>Options issued for commission on private placement $</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -38847,7 +38903,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -38946,7 +39006,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -39758,7 +39822,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -41390,7 +41458,11 @@
           <t>Shares issued for commission on private placement $</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
@@ -48931,7 +49003,11 @@
           <t>Deferred income tax recovery (Note 16)</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E410" t="inlineStr">
         <is>
           <t>-</t>
@@ -49814,7 +49890,11 @@
           <t>Deferred income tax recovery (Note 17)</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -54618,7 +54698,11 @@
           <t>Future income tax recovery (Note 14)</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr">
         <is>
           <t>-</t>
@@ -56018,7 +56102,11 @@
           <t>Future income tax recovery (Note 10)</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E481" t="inlineStr">
         <is>
           <t>-</t>
